--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ54"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2781,32 +2781,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133315934</v>
+        <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>80488</v>
+        <v>79476</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2819,10 +2819,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495732</v>
+        <v>495792</v>
       </c>
       <c r="R18" t="n">
-        <v>7037736</v>
+        <v>7037772</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2849,17 +2849,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en sälglåga.</t>
+          <t>Rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2879,22 +2879,22 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2911,42 +2911,50 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315934</t>
+          <t>https://artportalen.se/Sighting/136996327</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133315938</v>
+        <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>80488</v>
+        <v>79476</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2955,10 +2963,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>495565</v>
+        <v>495763</v>
       </c>
       <c r="R19" t="n">
-        <v>7037573</v>
+        <v>7037759</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,12 +2993,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3005,27 +3018,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3042,47 +3055,43 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315938</t>
+          <t>https://artportalen.se/Sighting/136996329</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133315939</v>
+        <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>80488</v>
+        <v>79476</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -3090,10 +3099,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>495555</v>
+        <v>495742</v>
       </c>
       <c r="R20" t="n">
-        <v>7037564</v>
+        <v>7037758</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3120,17 +3129,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg med soral.</t>
+          <t>Rätt så rikligt med garnlav på många granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3145,27 +3154,27 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3182,47 +3191,43 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315939</t>
+          <t>https://artportalen.se/Sighting/136996330</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133315940</v>
+        <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>80500</v>
+        <v>79476</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3230,10 +3235,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>495734</v>
+        <v>495701</v>
       </c>
       <c r="R21" t="n">
-        <v>7037731</v>
+        <v>7037795</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3260,17 +3265,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På en rönn.</t>
+          <t>En god mängd bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3290,22 +3295,22 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3322,47 +3327,43 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315940</t>
+          <t>https://artportalen.se/Sighting/136996331</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133315941</v>
+        <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>80500</v>
+        <v>79476</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3370,10 +3371,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>495733</v>
+        <v>495672</v>
       </c>
       <c r="R22" t="n">
-        <v>7037737</v>
+        <v>7037820</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3400,17 +3401,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en sälglåga.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3425,27 +3421,27 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på dött träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark of dead wood # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3462,16 +3458,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315941</t>
+          <t>https://artportalen.se/Sighting/136996332</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133315900</v>
+        <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>57975</v>
+        <v>79233</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3479,31 +3475,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3511,10 +3502,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>495727</v>
+        <v>495762</v>
       </c>
       <c r="R23" t="n">
-        <v>7037737</v>
+        <v>7037693</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3541,17 +3532,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på stambasen av en gran med spår av visst sav/kådaflöde.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3560,27 +3546,33 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Standing dead tree/snags # Med kolad ved. # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3597,16 +3589,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315900</t>
+          <t>https://artportalen.se/Sighting/136996277</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133315911</v>
+        <v>133315934</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3614,31 +3606,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3646,10 +3633,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>495622</v>
+        <v>495732</v>
       </c>
       <c r="R24" t="n">
-        <v>7037708</v>
+        <v>7037736</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3686,7 +3673,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3695,32 +3682,33 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3737,16 +3725,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315911</t>
+          <t>https://artportalen.se/Sighting/133315934</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133315912</v>
+        <v>133315938</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3754,31 +3742,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3786,10 +3769,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>495614</v>
+        <v>495565</v>
       </c>
       <c r="R25" t="n">
-        <v>7037710</v>
+        <v>7037573</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3824,17 +3807,13 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en gran.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3845,17 +3824,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3872,16 +3856,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315912</t>
+          <t>https://artportalen.se/Sighting/133315938</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133315913</v>
+        <v>133315939</v>
       </c>
       <c r="B26" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3889,29 +3873,28 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -3921,10 +3904,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>495587</v>
+        <v>495555</v>
       </c>
       <c r="R26" t="n">
-        <v>7037627</v>
+        <v>7037564</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3961,7 +3944,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, långt upp på en tall.</t>
+          <t>På sälg med soral.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3970,6 +3953,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3980,17 +3964,22 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -4007,46 +3996,45 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315913</t>
+          <t>https://artportalen.se/Sighting/133315939</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133315914</v>
+        <v>133315940</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -4056,10 +4044,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>495593</v>
+        <v>495734</v>
       </c>
       <c r="R27" t="n">
-        <v>7037607</v>
+        <v>7037731</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4096,7 +4084,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack, färska, längs flera meter på en gran.</t>
+          <t>På en rönn.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4105,32 +4093,33 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -4147,46 +4136,45 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315914</t>
+          <t>https://artportalen.se/Sighting/133315940</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133315915</v>
+        <v>133315941</v>
       </c>
       <c r="B28" t="n">
-        <v>57975</v>
+        <v>80500</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -4196,10 +4184,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>495589</v>
+        <v>495733</v>
       </c>
       <c r="R28" t="n">
-        <v>7037613</v>
+        <v>7037737</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4236,7 +4224,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på en gran.</t>
+          <t>På en sälglåga.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4245,6 +4233,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4255,22 +4244,22 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på dött träd</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark of dead wood # Salix caprea</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4287,13 +4276,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315915</t>
+          <t>https://artportalen.se/Sighting/133315941</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133315916</v>
+        <v>133315900</v>
       </c>
       <c r="B29" t="n">
         <v>57975</v>
@@ -4326,7 +4315,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -4336,10 +4325,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>495579</v>
+        <v>495727</v>
       </c>
       <c r="R29" t="n">
-        <v>7037617</v>
+        <v>7037737</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4376,7 +4365,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack, äldre, på stambasen av en gran med spår av visst sav/kådaflöde.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4390,7 +4379,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -4422,13 +4411,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315916</t>
+          <t>https://artportalen.se/Sighting/133315900</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133315917</v>
+        <v>133315911</v>
       </c>
       <c r="B30" t="n">
         <v>57975</v>
@@ -4471,10 +4460,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>495572</v>
+        <v>495622</v>
       </c>
       <c r="R30" t="n">
-        <v>7037628</v>
+        <v>7037708</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4511,7 +4500,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på en gran.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4538,9 +4527,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4557,13 +4551,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315917</t>
+          <t>https://artportalen.se/Sighting/133315911</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133315918</v>
+        <v>133315912</v>
       </c>
       <c r="B31" t="n">
         <v>57975</v>
@@ -4596,7 +4590,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4606,10 +4600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>495543</v>
+        <v>495614</v>
       </c>
       <c r="R31" t="n">
-        <v>7037573</v>
+        <v>7037710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4646,7 +4640,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack, färska, högt upp på en gran.</t>
+          <t>Ringhack, äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4673,14 +4667,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4697,13 +4686,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315918</t>
+          <t>https://artportalen.se/Sighting/133315912</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133315919</v>
+        <v>133315913</v>
       </c>
       <c r="B32" t="n">
         <v>57975</v>
@@ -4736,7 +4725,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -4746,10 +4735,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>495545</v>
+        <v>495587</v>
       </c>
       <c r="R32" t="n">
-        <v>7037553</v>
+        <v>7037627</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4786,7 +4775,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack, äldre, långt upp på en tall.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4805,22 +4794,17 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4837,13 +4821,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315919</t>
+          <t>https://artportalen.se/Sighting/133315913</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133315920</v>
+        <v>133315914</v>
       </c>
       <c r="B33" t="n">
         <v>57975</v>
@@ -4886,10 +4870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>495547</v>
+        <v>495593</v>
       </c>
       <c r="R33" t="n">
-        <v>7037525</v>
+        <v>7037607</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4926,7 +4910,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Ringhack, färska, långt upp på en tall.</t>
+          <t>Ringhack, färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4945,12 +4929,12 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -4960,7 +4944,7 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4977,13 +4961,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315920</t>
+          <t>https://artportalen.se/Sighting/133315914</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133315921</v>
+        <v>133315915</v>
       </c>
       <c r="B34" t="n">
         <v>57975</v>
@@ -5026,10 +5010,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>495549</v>
+        <v>495589</v>
       </c>
       <c r="R34" t="n">
-        <v>7037518</v>
+        <v>7037613</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -5117,13 +5101,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315921</t>
+          <t>https://artportalen.se/Sighting/133315915</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133315922</v>
+        <v>133315916</v>
       </c>
       <c r="B35" t="n">
         <v>57975</v>
@@ -5166,10 +5150,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>495555</v>
+        <v>495579</v>
       </c>
       <c r="R35" t="n">
-        <v>7037504</v>
+        <v>7037617</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5206,7 +5190,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5223,11 +5207,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Barrblandskog med tall och gran.</t>
-        </is>
-      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>gran</t>
@@ -5238,14 +5217,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -5262,13 +5236,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315922</t>
+          <t>https://artportalen.se/Sighting/133315916</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133315923</v>
+        <v>133315917</v>
       </c>
       <c r="B36" t="n">
         <v>57975</v>
@@ -5301,7 +5275,7 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -5311,10 +5285,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>495568</v>
+        <v>495572</v>
       </c>
       <c r="R36" t="n">
-        <v>7037491</v>
+        <v>7037628</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5351,7 +5325,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
+          <t>Ringhack, färska och äldre, på en gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5378,14 +5352,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -5402,13 +5371,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315923</t>
+          <t>https://artportalen.se/Sighting/133315917</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133315924</v>
+        <v>133315918</v>
       </c>
       <c r="B37" t="n">
         <v>57975</v>
@@ -5441,7 +5410,7 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -5451,10 +5420,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>495636</v>
+        <v>495543</v>
       </c>
       <c r="R37" t="n">
-        <v>7037503</v>
+        <v>7037573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5491,7 +5460,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, enstaka högt upp på en tall.</t>
+          <t>Ringhack, färska, högt upp på en gran.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5510,12 +5479,12 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -5525,7 +5494,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5542,48 +5511,48 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315924</t>
+          <t>https://artportalen.se/Sighting/133315918</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133315943</v>
+        <v>133315919</v>
       </c>
       <c r="B38" t="n">
-        <v>111153</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220240</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -5591,10 +5560,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>495656</v>
+        <v>495545</v>
       </c>
       <c r="R38" t="n">
-        <v>7037779</v>
+        <v>7037553</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5629,19 +5598,43 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack (savhack), färska, på en gran.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5658,56 +5651,48 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315943</t>
+          <t>https://artportalen.se/Sighting/133315919</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133315945</v>
+        <v>133315920</v>
       </c>
       <c r="B39" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5715,10 +5700,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>495677</v>
+        <v>495547</v>
       </c>
       <c r="R39" t="n">
-        <v>7037554</v>
+        <v>7037525</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5745,17 +5730,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Minst 25 plantor inom ca 1 m2 yta.</t>
+          <t>Ringhack, färska, långt upp på en tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5764,13 +5749,32 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
@@ -5787,56 +5791,48 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315945</t>
+          <t>https://artportalen.se/Sighting/133315920</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133315946</v>
+        <v>133315921</v>
       </c>
       <c r="B40" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5844,10 +5840,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>495707</v>
+        <v>495549</v>
       </c>
       <c r="R40" t="n">
-        <v>7037627</v>
+        <v>7037518</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5874,17 +5870,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 1,5 m2 yta.</t>
+          <t>Ringhack, färska, på en gran.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5893,13 +5889,32 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5916,71 +5931,59 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315946</t>
+          <t>https://artportalen.se/Sighting/133315921</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133315947</v>
+        <v>133315922</v>
       </c>
       <c r="B41" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>495698</v>
+        <v>495555</v>
       </c>
       <c r="R41" t="n">
-        <v>7037636</v>
+        <v>7037504</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -6007,17 +6010,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Minst 33 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, färska och äldre, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -6026,13 +6029,37 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Barrblandskog med tall och gran.</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -6049,56 +6076,48 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315947</t>
+          <t>https://artportalen.se/Sighting/133315922</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133315948</v>
+        <v>133315923</v>
       </c>
       <c r="B42" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -6106,10 +6125,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>495621</v>
+        <v>495568</v>
       </c>
       <c r="R42" t="n">
-        <v>7037632</v>
+        <v>7037491</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6146,7 +6165,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Minst 4 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, med kådaflöden på en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6155,13 +6174,32 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -6178,56 +6216,48 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315948</t>
+          <t>https://artportalen.se/Sighting/133315923</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133315949</v>
+        <v>133315924</v>
       </c>
       <c r="B43" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
@@ -6235,10 +6265,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>495648</v>
+        <v>495636</v>
       </c>
       <c r="R43" t="n">
-        <v>7037599</v>
+        <v>7037503</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6275,7 +6305,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
+          <t>Ringhack, äldre, enstaka högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6284,13 +6314,32 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -6307,56 +6356,48 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315949</t>
+          <t>https://artportalen.se/Sighting/133315924</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133315951</v>
+        <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>58008</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6364,10 +6405,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>495631</v>
+        <v>495759</v>
       </c>
       <c r="R44" t="n">
-        <v>7037575</v>
+        <v>7037767</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6394,32 +6435,51 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+          <t>Vedsvampsrötad granhögstubbe med ett påbörjat bohål (diameter 40 - 45 mm) men inte färdiguthackat på ca 2 meters höjd och ett möjligen färdiguthackat och använt bohål högre upp i granhögstubben. Inte helt säkra spår efter tretåig hackspett men då det finns ringhack av tretåig hackspett och höga livsmiljövärden för arten i samma skogsbestånd är det troligt att hackspåren är skapade av denna hackspettsart.</t>
         </is>
       </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -6436,56 +6496,52 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315951</t>
+          <t>https://artportalen.se/Sighting/136996198</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133315952</v>
+        <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>99195</v>
+        <v>58169</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6497,10 +6553,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>495622</v>
+        <v>495679</v>
       </c>
       <c r="R45" t="n">
-        <v>7037566</v>
+        <v>7037840</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6527,17 +6583,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Minst 17 plantor inom ca 0,5 m2 yta.</t>
+          <t>Minst 1 talltita med lockläte observerades i äldre flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6546,18 +6602,12 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>Barrblandskog av gran och tall med inslag av asp, björk och sälg.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6574,71 +6624,59 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315952</t>
+          <t>https://artportalen.se/Sighting/136996201</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133315953</v>
+        <v>133315943</v>
       </c>
       <c r="B46" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>495579</v>
+        <v>495656</v>
       </c>
       <c r="R46" t="n">
-        <v>7037546</v>
+        <v>7037779</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6673,11 +6711,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -6690,7 +6723,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6707,71 +6740,59 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315953</t>
+          <t>https://artportalen.se/Sighting/133315943</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133315954</v>
+        <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>99195</v>
+        <v>111332</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>495618</v>
+        <v>495687</v>
       </c>
       <c r="R47" t="n">
-        <v>7037521</v>
+        <v>7037766</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6798,17 +6819,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor inom ca 1,5 m2 yta.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6823,7 +6839,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr"/>
@@ -6840,71 +6856,59 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315954</t>
+          <t>https://artportalen.se/Sighting/136996272</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133315955</v>
+        <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>99195</v>
+        <v>111332</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>495605</v>
+        <v>495709</v>
       </c>
       <c r="R48" t="n">
-        <v>7037578</v>
+        <v>7037794</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6931,17 +6935,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Minst 14 plantor och 1 vinterståndare inom ca 1,5 m2 yta.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6956,7 +6955,7 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6973,50 +6972,42 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315955</t>
+          <t>https://artportalen.se/Sighting/136996273</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133315956</v>
+        <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>99195</v>
+        <v>111332</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -7030,10 +7021,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>495665</v>
+        <v>495669</v>
       </c>
       <c r="R49" t="n">
-        <v>7037578</v>
+        <v>7037824</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -7060,17 +7051,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Minst 5 plantor inom ca 0,5 m2 yta.</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -7085,7 +7071,7 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -7102,13 +7088,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315956</t>
+          <t>https://artportalen.se/Sighting/136996274</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133315957</v>
+        <v>133315945</v>
       </c>
       <c r="B50" t="n">
         <v>99195</v>
@@ -7138,7 +7124,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -7152,21 +7138,17 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>495673</v>
+        <v>495677</v>
       </c>
       <c r="R50" t="n">
-        <v>7037599</v>
+        <v>7037554</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7193,17 +7175,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Minst 50 plantor inom ca 1,5 m2 yta i barrblandskog.</t>
+          <t>Minst 25 plantor inom ca 1 m2 yta.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7235,13 +7217,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315957</t>
+          <t>https://artportalen.se/Sighting/133315945</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133315958</v>
+        <v>133315946</v>
       </c>
       <c r="B51" t="n">
         <v>99195</v>
@@ -7271,7 +7253,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -7285,21 +7267,17 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Erik-Nilsabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>495724</v>
+        <v>495707</v>
       </c>
       <c r="R51" t="n">
-        <v>7037681</v>
+        <v>7037627</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7326,17 +7304,17 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Minst 60 vitala plantor och 2 vinterståndare inom ca 2 m2 yta i  barrblandskog.</t>
+          <t>Minst 17 plantor inom ca 1,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7368,13 +7346,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315958</t>
+          <t>https://artportalen.se/Sighting/133315946</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133315959</v>
+        <v>133315947</v>
       </c>
       <c r="B52" t="n">
         <v>99195</v>
@@ -7404,7 +7382,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7429,10 +7407,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>495734</v>
+        <v>495698</v>
       </c>
       <c r="R52" t="n">
-        <v>7037728</v>
+        <v>7037636</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7459,17 +7437,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Minst 25 plantor och 2 vinterståndare inom ca 0,5 m2 yta i granskog, intill en rönn med luddlav.</t>
+          <t>Minst 33 plantor och 1 vinterståndare inom ca 0,5 m2 yta.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7484,7 +7462,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -7501,43 +7479,55 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315959</t>
+          <t>https://artportalen.se/Sighting/133315947</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133315933</v>
+        <v>133315948</v>
       </c>
       <c r="B53" t="n">
-        <v>98066</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
@@ -7546,10 +7536,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>495612</v>
+        <v>495621</v>
       </c>
       <c r="R53" t="n">
-        <v>7037520</v>
+        <v>7037632</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7584,6 +7574,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -7599,11 +7594,6 @@
           <t>Barrskog</t>
         </is>
       </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
-        </is>
-      </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
@@ -7618,43 +7608,55 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133315933</t>
+          <t>https://artportalen.se/Sighting/133315948</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133315931</v>
+        <v>133315949</v>
       </c>
       <c r="B54" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
@@ -7663,10 +7665,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>495576</v>
+        <v>495648</v>
       </c>
       <c r="R54" t="n">
-        <v>7037550</v>
+        <v>7037599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7701,6 +7703,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -7730,7 +7737,2087 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133315949</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>133315951</v>
+      </c>
+      <c r="B55" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>495631</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7037575</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315951</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>133315952</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>495622</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7037566</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Minst 17 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Barrblandskog av gran och tall med inslag av asp, björk och sälg.</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315952</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>133315953</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>495579</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7037546</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Minst 7 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315953</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>133315954</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>495618</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7037521</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315954</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>133315955</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>495605</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7037578</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Minst 14 plantor och 1 vinterståndare inom ca 1,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315955</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>133315956</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>495665</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7037578</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Minst 5 plantor inom ca 0,5 m2 yta.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315956</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>133315957</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>495673</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7037599</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Minst 50 plantor inom ca 1,5 m2 yta i barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315957</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>133315958</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>495724</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7037681</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Minst 60 vitala plantor och 2 vinterståndare inom ca 2 m2 yta i  barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315958</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>133315959</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>495734</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7037728</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 2 vinterståndare inom ca 0,5 m2 yta i granskog, intill en rönn med luddlav.</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315959</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136996279</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>495652</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7037776</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor inom ca 0,5 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136996279</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136996280</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>495680</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7037773</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Minst 4 plantor och 2 överblommade blomställningar inom ca 0,5 m2 yta i äldre granskog. Växer bland stor björnmossa och kammossa.</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136996280</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136996282</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>495670</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7037802</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Minst 25 plantor och 16 överblommade blomställningar inom ca 4 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136996282</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136996283</v>
+      </c>
+      <c r="B67" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>495666</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7037823</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Minst 90 plantor och 27 överblommade blomställningar inom ca 5 m2 yta i äldre granskog.</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136996283</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>133315933</v>
+      </c>
+      <c r="B68" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>495612</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7037520</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133315933</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>133315931</v>
+      </c>
+      <c r="B69" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>495576</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7037550</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/133315931</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136996222</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79234</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Erik-Nilsabodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>495759</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7037690</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Rikligt på en kolad tallhögstubbe.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog och granskog med flera kolade högstubbar som indikerar tidigare brand.</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Med kolad ved. # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136996222</t>
         </is>
       </c>
     </row>
@@ -7789,6 +9876,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6749,7 +6749,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6393,11 +6393,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -6537,11 +6533,7 @@
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6776,11 +6768,7 @@
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
@@ -6892,11 +6880,7 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -7008,11 +6992,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -8975,11 +8955,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -9104,11 +9080,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -9233,11 +9205,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -9362,11 +9330,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79293</v>
+        <v>79294</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/A 17267-2026 artfynd.xlsx
+++ b/artfynd/A 17267-2026 artfynd.xlsx
@@ -2784,7 +2784,7 @@
         <v>136996327</v>
       </c>
       <c r="B18" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>136996329</v>
       </c>
       <c r="B19" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>136996330</v>
       </c>
       <c r="B20" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>136996331</v>
       </c>
       <c r="B21" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>136996332</v>
       </c>
       <c r="B22" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>136996277</v>
       </c>
       <c r="B23" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         <v>136996198</v>
       </c>
       <c r="B44" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136996201</v>
       </c>
       <c r="B45" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>136996272</v>
       </c>
       <c r="B47" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>136996273</v>
       </c>
       <c r="B48" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>136996274</v>
       </c>
       <c r="B49" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>136996279</v>
       </c>
       <c r="B64" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>136996280</v>
       </c>
       <c r="B65" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         <v>136996282</v>
       </c>
       <c r="B66" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -9295,7 +9295,7 @@
         <v>136996283</v>
       </c>
       <c r="B67" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>136996222</v>
       </c>
       <c r="B70" t="n">
-        <v>79294</v>
+        <v>79297</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
